--- a/Dashboards/data/Data final/ingresos/ingresos_area.xlsx
+++ b/Dashboards/data/Data final/ingresos/ingresos_area.xlsx
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>243.7</v>
+        <v>246.59</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>130.43</v>
+        <v>135.03</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>262.64</v>
+        <v>262.35</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>135.59</v>
+        <v>141.2</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>255.85</v>
+        <v>254.06</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>142.77</v>
+        <v>148.44</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>256.59</v>
+        <v>242.6</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>140.53</v>
+        <v>143.38</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>270.91</v>
+        <v>280.13</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>152.47</v>
+        <v>170.7</v>
       </c>
     </row>
     <row r="46">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>207.49</v>
+        <v>210.94</v>
       </c>
     </row>
     <row r="64">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>222.21</v>
+        <v>223.77</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>219.83</v>
+        <v>220.42</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>219.7</v>
+        <v>211.07</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>233.23</v>
+        <v>245.33</v>
       </c>
     </row>
   </sheetData>
